--- a/resultados/agudosdosul/erros_varredura.xlsx
+++ b/resultados/agudosdosul/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2240,6 +2240,118 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>agudosdosul</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>http://www.agudosdosul.pr.gov.br/rreo-e-rgf/rreo-e-rgf-2024/2-semestre-2024/1005-anexo-02-demonstrativo-da-dvida-consolidada-lquida-2o-semestre-2024-1/file</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>404</v>
+      </c>
+      <c r="E66" t="n">
+        <v>8</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:54:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>agudosdosul</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>http://www.agudosdosul.pr.gov.br/pre-cadastro-para-o-projeto-castrapet</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>404</v>
+      </c>
+      <c r="E67" t="n">
+        <v>8</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:12:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>agudosdosul</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>http://www.agudosdosul.pr.gov.br/pre-cadastro-para-o-transporte-universitario</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>404</v>
+      </c>
+      <c r="E68" t="n">
+        <v>8</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>agudosdosul</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>http://www.agudosdosul.pr.gov.br/inscricoes-show-de-talentos</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>404</v>
+      </c>
+      <c r="E69" t="n">
+        <v>9</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:25:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
